--- a/astro-site/public/dl/kit-tareas-hotel/11-piscina.xlsx
+++ b/astro-site/public/dl/kit-tareas-hotel/11-piscina.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Apertura Piscina" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cierre Piscina" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mant. Semanal" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Servicio Toallas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apertura Piscina" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Piscina" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mant. Semanal" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servicio Toallas" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura Piscina'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cierre Piscina'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mant. Semanal'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Servicio Toallas'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -83,6 +88,11 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -140,48 +150,59 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -541,15 +562,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -557,6 +579,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -585,9 +608,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -609,8 +630,25 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hotel · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -619,18 +657,18 @@
   <sheetPr>
     <tabColor rgb="00E0F7FA"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -647,6 +685,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -767,6 +806,7 @@
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="13" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -886,6 +926,26 @@
       <c r="E16" s="12" t="n"/>
       <c r="F16" s="11" t="n"/>
       <c r="G16" s="13" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C17">
+        <f>COUNTIF(E6:E16,"✓")</f>
+        <v>1.0</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E17">
+        <f>COUNTIF(B6:B16,"?*")</f>
+        <v>9.0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
@@ -910,12 +970,26 @@
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G16">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E13 E14 E15 E16" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -924,18 +998,18 @@
   <sheetPr>
     <tabColor rgb="00E0F7FA"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -952,6 +1026,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1128,6 +1203,26 @@
       <c r="E12" s="12" t="n"/>
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="13" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>COUNTIF(E6:E12,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E13">
+        <f>COUNTIF(B6:B12,"?*")</f>
+        <v>7.0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -1151,12 +1246,26 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A14:G14"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G12">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1165,18 +1274,18 @@
   <sheetPr>
     <tabColor rgb="00E0F7FA"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1193,6 +1302,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1369,6 +1479,26 @@
       <c r="E12" s="12" t="n"/>
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="13" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>COUNTIF(E6:E12,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E13">
+        <f>COUNTIF(B6:B12,"?*")</f>
+        <v>7.0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -1392,12 +1522,26 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A14:G14"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G12">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1406,18 +1550,18 @@
   <sheetPr>
     <tabColor rgb="00E0F7FA"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1434,6 +1578,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1591,6 +1736,26 @@
       <c r="E11" s="12" t="n"/>
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="13" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C12">
+        <f>COUNTIF(E6:E11,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E12">
+        <f>COUNTIF(B6:B11,"?*")</f>
+        <v>6.0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -1614,11 +1779,25 @@
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A13:G13"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G11">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-hotel/11-piscina.xlsx
+++ b/astro-site/public/dl/kit-tareas-hotel/11-piscina.xlsx
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -634,7 +634,14 @@
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hotel · info@aichef.pro</t>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-hotel · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -934,8 +941,8 @@
         </is>
       </c>
       <c r="C17">
-        <f>COUNTIF(E6:E16,"✓")</f>
-        <v>1.0</v>
+        <f>COUNTIFS(B6:B16,"?*",E6:E16,"✓")-COUNTIFS(B6:B16,"Tarea",E6:E16,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -943,8 +950,8 @@
         </is>
       </c>
       <c r="E17">
-        <f>COUNTIF(B6:B16,"?*")</f>
-        <v>9.0</v>
+        <f>COUNTIF(B6:B16,"?*")-COUNTIF(B6:B16,"Tarea")-COUNTIF(E6:E16,"N/A")</f>
+        <v>8.0</v>
       </c>
     </row>
     <row r="18">
@@ -976,8 +983,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1211,7 +1218,7 @@
         </is>
       </c>
       <c r="C13">
-        <f>COUNTIF(E6:E12,"✓")</f>
+        <f>COUNTIFS(B6:B12,"?*",E6:E12,"✓")-COUNTIFS(B6:B12,"Tarea",E6:E12,"✓")</f>
         <v>0.0</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -1220,7 +1227,7 @@
         </is>
       </c>
       <c r="E13">
-        <f>COUNTIF(B6:B12,"?*")</f>
+        <f>COUNTIF(B6:B12,"?*")-COUNTIF(B6:B12,"Tarea")-COUNTIF(E6:E12,"N/A")</f>
         <v>7.0</v>
       </c>
     </row>
@@ -1252,8 +1259,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1487,7 +1494,7 @@
         </is>
       </c>
       <c r="C13">
-        <f>COUNTIF(E6:E12,"✓")</f>
+        <f>COUNTIFS(B6:B12,"?*",E6:E12,"✓")-COUNTIFS(B6:B12,"Tarea",E6:E12,"✓")</f>
         <v>0.0</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -1496,7 +1503,7 @@
         </is>
       </c>
       <c r="E13">
-        <f>COUNTIF(B6:B12,"?*")</f>
+        <f>COUNTIF(B6:B12,"?*")-COUNTIF(B6:B12,"Tarea")-COUNTIF(E6:E12,"N/A")</f>
         <v>7.0</v>
       </c>
     </row>
@@ -1528,8 +1535,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1744,7 +1751,7 @@
         </is>
       </c>
       <c r="C12">
-        <f>COUNTIF(E6:E11,"✓")</f>
+        <f>COUNTIFS(B6:B11,"?*",E6:E11,"✓")-COUNTIFS(B6:B11,"Tarea",E6:E11,"✓")</f>
         <v>0.0</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -1753,7 +1760,7 @@
         </is>
       </c>
       <c r="E12">
-        <f>COUNTIF(B6:B11,"?*")</f>
+        <f>COUNTIF(B6:B11,"?*")-COUNTIF(B6:B11,"Tarea")-COUNTIF(E6:E11,"N/A")</f>
         <v>6.0</v>
       </c>
     </row>
@@ -1785,8 +1792,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
